--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484733_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484733_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.7309</v>
+        <v>10.5536</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9364</v>
+        <v>11.521</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2055</v>
+        <v>-0.9675</v>
       </c>
       <c r="G2" t="n">
         <v>9.440200000000001</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5961</v>
+        <v>0.2266</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0335</v>
+        <v>-0.4489</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4374</v>
+        <v>0.6755</v>
       </c>
       <c r="V2" t="n">
         <v>1.2642</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.228999999999999</v>
+        <v>7.2753</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2265</v>
+        <v>4.9342</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0025</v>
+        <v>2.3411</v>
       </c>
       <c r="G3" t="n">
         <v>3.4807</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9746</v>
+        <v>2.0209</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5596</v>
+        <v>0.2673</v>
       </c>
       <c r="U3" t="n">
-        <v>2.415</v>
+        <v>1.7536</v>
       </c>
       <c r="V3" t="n">
         <v>1.585</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4547</v>
+        <v>2.212</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4274</v>
+        <v>0.317</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0273</v>
+        <v>1.895</v>
       </c>
       <c r="G4" t="n">
         <v>-3.9804</v>
@@ -766,13 +766,13 @@
         <v>3.2079</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2844</v>
+        <v>1.0417</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9769</v>
+        <v>-0.1336</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3075</v>
+        <v>1.1752</v>
       </c>
       <c r="V4" t="n">
         <v>3.075</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6194</v>
+        <v>1.9827</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8134</v>
+        <v>1.2031</v>
       </c>
       <c r="F5" t="n">
-        <v>0.806</v>
+        <v>0.7796</v>
       </c>
       <c r="G5" t="n">
         <v>1.314</v>
@@ -844,13 +844,13 @@
         <v>0.7548</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1475</v>
+        <v>0.2157</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.2569</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4991</v>
+        <v>0.4727</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3018</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5304</v>
+        <v>0.5363</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7951</v>
+        <v>-0.1517</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2647</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9647</v>
@@ -1000,13 +1000,13 @@
         <v>1.887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5655</v>
+        <v>0.5011</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0335</v>
+        <v>-0.3901</v>
       </c>
       <c r="U7" t="n">
-        <v>0.468</v>
+        <v>0.8913</v>
       </c>
       <c r="V7" t="n">
         <v>2.1886</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-0.4149</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.43</v>
+        <v>-0.5661</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1662</v>
+        <v>0.1512</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2761</v>
@@ -1078,13 +1078,13 @@
         <v>2.0757</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9053</v>
+        <v>-0.724</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4674</v>
+        <v>-0.6035</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4379</v>
+        <v>-0.1205</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3018</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4054</v>
+        <v>-1.0518</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4704</v>
+        <v>-1.2755</v>
       </c>
       <c r="F9" t="n">
-        <v>0.065</v>
+        <v>0.2237</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7688</v>
@@ -1156,13 +1156,13 @@
         <v>0.1887</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1182</v>
+        <v>0.4717</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1052</v>
+        <v>0.0896</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2234</v>
+        <v>0.3821</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2055</v>
+        <v>-2.5532</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7957</v>
+        <v>-3.9318</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5902</v>
+        <v>1.3786</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0375</v>
@@ -1234,13 +1234,13 @@
         <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5302</v>
+        <v>0.1825</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1147</v>
+        <v>-0.2508</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6449</v>
+        <v>0.4333</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4292</v>
+        <v>-2.677</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5372</v>
+        <v>-3.732</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1079</v>
+        <v>1.055</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8048</v>
@@ -1312,13 +1312,13 @@
         <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>0.602</v>
+        <v>0.3542</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0436</v>
+        <v>-0.2384</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6455</v>
+        <v>0.5926</v>
       </c>
       <c r="V11" t="n">
         <v>0.3398</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.149</v>
+        <v>-4.8509</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8042</v>
+        <v>-4.4531</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3448</v>
+        <v>-0.3977</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6064</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1087</v>
+        <v>-0.8105</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2345</v>
+        <v>-0.8834</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1259</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.6691</v>
+        <v>11.963</v>
       </c>
       <c r="E13" t="n">
-        <v>4.522000000000002</v>
+        <v>4.816000000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>7.1471</v>
+        <v>7.146999999999998</v>
       </c>
       <c r="G13" t="n">
         <v>-1.252899999999998</v>
@@ -1468,13 +1468,13 @@
         <v>16.0395</v>
       </c>
       <c r="S13" t="n">
-        <v>3.186300000000001</v>
+        <v>3.4799</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1426</v>
+        <v>-2.8487</v>
       </c>
       <c r="U13" t="n">
-        <v>6.3288</v>
+        <v>6.3287</v>
       </c>
       <c r="V13" t="n">
         <v>7.849</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4231</v>
+        <v>3.1717</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6004</v>
+        <v>2.1133</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8227</v>
+        <v>1.0584</v>
       </c>
       <c r="G14" t="n">
         <v>2.772</v>
@@ -1546,13 +1546,13 @@
         <v>1.887</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3304</v>
+        <v>0.0789</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0994</v>
+        <v>-0.5866</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4298</v>
+        <v>0.6655</v>
       </c>
       <c r="V14" t="n">
         <v>0.3208</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. TAENO ELEZ</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5108</v>
+        <v>-0.0468</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4364</v>
+        <v>-1.006</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9472</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>2.175</v>
+        <v>-1.1017</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2633</v>
+        <v>3.4035</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0883</v>
+        <v>-4.5053</v>
       </c>
       <c r="J17" t="n">
-        <v>5.289</v>
+        <v>0.8102</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8409</v>
+        <v>3.9091</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4481</v>
+        <v>-3.0989</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.114</v>
+        <v>-1.9119</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5777</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5363</v>
+        <v>-1.4064</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.887</v>
+        <v>1.3209</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4844</v>
+        <v>-0.266</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0407</v>
+        <v>-0.8727</v>
       </c>
       <c r="U17" t="n">
-        <v>0.525</v>
+        <v>0.6068</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2832</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>M. TAENO ELEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6555</v>
+        <v>-0.9209000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5907</v>
+        <v>0.9492</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9351</v>
+        <v>-1.8702</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1017</v>
+        <v>2.175</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4035</v>
+        <v>2.2633</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.5053</v>
+        <v>-0.0883</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8102</v>
+        <v>5.289</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9091</v>
+        <v>3.8409</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.0989</v>
+        <v>1.4481</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9119</v>
+        <v>-3.114</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-1.5777</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4064</v>
+        <v>-1.5363</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3209</v>
+        <v>-1.887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8747</v>
+        <v>0.0742</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4574</v>
+        <v>-0.5278</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5827</v>
+        <v>0.602</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2832</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4526</v>
+        <v>-0.9342</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4948</v>
+        <v>-1.3974</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0422</v>
+        <v>0.4631</v>
       </c>
       <c r="G19" t="n">
         <v>1.7084</v>
@@ -1936,13 +1936,13 @@
         <v>0.9435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.454</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7055</v>
+        <v>-0.608</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2669</v>
+        <v>0.154</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2452</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.602</v>
+        <v>-1.6043</v>
       </c>
       <c r="E20" t="n">
         <v>-1.3365</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2655</v>
+        <v>-0.2678</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5075</v>
@@ -2014,13 +2014,13 @@
         <v>0.5661</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.679</v>
+        <v>-0.6813</v>
       </c>
       <c r="T20" t="n">
         <v>-0.823</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1441</v>
+        <v>0.1417</v>
       </c>
       <c r="V20" t="n">
         <v>0.9054</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1591</v>
+        <v>-1.9147</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5397</v>
+        <v>-4.0526</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3807</v>
+        <v>2.1379</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4655</v>
@@ -2092,13 +2092,13 @@
         <v>1.5096</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3162</v>
+        <v>-0.0718</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3521</v>
+        <v>-0.8649</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0359</v>
+        <v>0.7931</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.501</v>
+        <v>-2.0908</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7631</v>
+        <v>-1.6656</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7379</v>
+        <v>-0.4252</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9659</v>
@@ -2170,13 +2170,13 @@
         <v>2.8305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.271</v>
+        <v>0.1392</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9254</v>
+        <v>-0.8279</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6544</v>
+        <v>0.9671</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2076</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2854</v>
+        <v>-3.9258</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7506</v>
+        <v>-0.6532</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5348</v>
+        <v>-3.2726</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2454</v>
@@ -2248,13 +2248,13 @@
         <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8894</v>
+        <v>-0.5298</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8818</v>
+        <v>-0.7844</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0076</v>
+        <v>0.2546</v>
       </c>
       <c r="V23" t="n">
         <v>-3.094</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7445</v>
+        <v>-4.9226</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5271</v>
+        <v>-2.9168</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2174</v>
+        <v>-2.0058</v>
       </c>
       <c r="G24" t="n">
         <v>-2.9349</v>
@@ -2326,13 +2326,13 @@
         <v>1.3209</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0017</v>
+        <v>-0.1764</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0436</v>
+        <v>-0.4333</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0453</v>
+        <v>0.2569</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2452</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.6691</v>
+        <v>-10.3697</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.147</v>
+        <v>-7.1469</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.5221</v>
+        <v>-3.223</v>
       </c>
       <c r="G25" t="n">
         <v>1.253200000000001</v>
@@ -2395,7 +2395,7 @@
         <v>-4.541700000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.887</v>
+        <v>-1.886999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-16.0395</v>
@@ -2404,13 +2404,13 @@
         <v>14.1525</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.1861</v>
+        <v>-1.887</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.3289</v>
+        <v>-6.3286</v>
       </c>
       <c r="U25" t="n">
-        <v>3.1427</v>
+        <v>4.4417</v>
       </c>
       <c r="V25" t="n">
         <v>-7.849</v>
